--- a/research/traditional_assets/database/data/argentina/argentina_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_engineering_construction.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +587,26 @@
           <t>Engineering/Construction</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.271</v>
+      </c>
+      <c r="G2">
+        <v>-0.07503782148260213</v>
+      </c>
+      <c r="H2">
+        <v>-0.07503782148260213</v>
+      </c>
+      <c r="I2">
+        <v>-0.08950075642965205</v>
+      </c>
+      <c r="J2">
+        <v>-0.08950075642965205</v>
+      </c>
       <c r="K2">
-        <v>0.297</v>
+        <v>-9.703999999999999</v>
+      </c>
+      <c r="L2">
+        <v>-0.1468078668683812</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,28 +624,22 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>-0.3074534161490683</v>
+        <v>6.843221788818177e-05</v>
       </c>
       <c r="X2">
-        <v>0.2347981492167851</v>
-      </c>
-      <c r="Y2">
-        <v>-0.5422515653658534</v>
+        <v>0.2108498602151804</v>
       </c>
       <c r="AB2">
-        <v>0.2347981492167851</v>
+        <v>0.2108498602151804</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -639,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -648,22 +660,28 @@
         <v>-0</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-6.84369011771147e-05</v>
       </c>
       <c r="AK2">
-        <v>-0</v>
+        <v>0.001869158878504673</v>
       </c>
       <c r="AL2">
-        <v>0.04</v>
+        <v>5.05</v>
       </c>
       <c r="AM2">
-        <v>0.04</v>
+        <v>3.889</v>
+      </c>
+      <c r="AN2">
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-1.675</v>
+        <v>-1.171485148514852</v>
+      </c>
+      <c r="AP2">
+        <v>0.0002016129032258065</v>
       </c>
       <c r="AQ2">
-        <v>-1.675</v>
+        <v>-1.521213679609154</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +701,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.297</v>
+        <v>0.396</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -707,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.001095290251916758</v>
       </c>
       <c r="W3">
-        <v>-0.3074534161490683</v>
+        <v>-0.423982869379015</v>
       </c>
       <c r="X3">
-        <v>0.2347981492167851</v>
+        <v>0.2108498602151804</v>
       </c>
       <c r="Y3">
-        <v>-0.5422515653658534</v>
+        <v>-0.6348327295941953</v>
       </c>
       <c r="AB3">
-        <v>0.2347981492167851</v>
+        <v>0.2108498602151804</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -734,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -743,22 +761,126 @@
         <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.001096491228070175</v>
       </c>
       <c r="AK3">
-        <v>-0</v>
+        <v>0.001869158878504673</v>
       </c>
       <c r="AL3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.04</v>
-      </c>
-      <c r="AO3">
-        <v>-1.675</v>
+        <v>-0.031</v>
       </c>
       <c r="AQ3">
-        <v>-1.675</v>
+        <v>1.806451612903226</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DYCASA Sociedad Anónima (BASE:DYCA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engineering/Construction</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.271</v>
+      </c>
+      <c r="G4">
+        <v>-0.07503782148260213</v>
+      </c>
+      <c r="H4">
+        <v>-0.07503782148260213</v>
+      </c>
+      <c r="I4">
+        <v>-0.0886535552193646</v>
+      </c>
+      <c r="J4">
+        <v>-0.0886535552193646</v>
+      </c>
+      <c r="K4">
+        <v>-10.1</v>
+      </c>
+      <c r="L4">
+        <v>-0.1527987897125567</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0.2108498602151804</v>
+      </c>
+      <c r="AB4">
+        <v>0.2108498602151804</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>5.05</v>
+      </c>
+      <c r="AM4">
+        <v>3.92</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AO4">
+        <v>-1.160396039603961</v>
+      </c>
+      <c r="AP4">
+        <v>-0</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.494897959183674</v>
       </c>
     </row>
   </sheetData>
